--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DFS_HRM-2031-0260/panel_11/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DFS_HRM-2031-0260/panel_11/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.70594</v>
+        <v>16.96761</v>
       </c>
       <c r="D2" t="n">
-        <v>16.62722</v>
+        <v>16.57394</v>
       </c>
       <c r="E2" t="n">
-        <v>16.56566</v>
+        <v>16.62233</v>
       </c>
       <c r="F2" t="n">
-        <v>42.48647</v>
+        <v>42.99155</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05031</v>
+        <v>0.04985</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81057</v>
+        <v>1.82828</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.65999</v>
+        <v>16.69975</v>
       </c>
       <c r="D3" t="n">
-        <v>16.65655</v>
+        <v>16.48192</v>
       </c>
       <c r="E3" t="n">
-        <v>16.81578</v>
+        <v>16.69064</v>
       </c>
       <c r="F3" t="n">
-        <v>43.03021</v>
+        <v>42.72007</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05076</v>
+        <v>0.05062</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80535</v>
+        <v>1.781</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.76265</v>
+        <v>16.77968</v>
       </c>
       <c r="D4" t="n">
-        <v>16.35252</v>
+        <v>16.34433</v>
       </c>
       <c r="E4" t="n">
-        <v>16.55298</v>
+        <v>16.6987</v>
       </c>
       <c r="F4" t="n">
-        <v>42.05989</v>
+        <v>42.01129</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0497</v>
+        <v>0.05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.77457</v>
+        <v>1.82355</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.48768</v>
+        <v>16.68598</v>
       </c>
       <c r="D6" t="n">
-        <v>16.26748</v>
+        <v>15.96523</v>
       </c>
       <c r="E6" t="n">
-        <v>16.30249</v>
+        <v>16.30639</v>
       </c>
       <c r="F6" t="n">
-        <v>21.54071</v>
+        <v>22.0441</v>
       </c>
       <c r="G6" t="n">
-        <v>33.6601</v>
+        <v>33.53589</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.86496</v>
+        <v>16.64025</v>
       </c>
       <c r="D7" t="n">
-        <v>15.96194</v>
+        <v>15.84054</v>
       </c>
       <c r="E7" t="n">
-        <v>16.30501</v>
+        <v>16.3238</v>
       </c>
       <c r="F7" t="n">
-        <v>21.59681</v>
+        <v>21.43561</v>
       </c>
       <c r="G7" t="n">
-        <v>34.27927</v>
+        <v>34.09837</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.65997</v>
+        <v>16.6439</v>
       </c>
       <c r="D8" t="n">
-        <v>15.84171</v>
+        <v>15.93978</v>
       </c>
       <c r="E8" t="n">
-        <v>16.16696</v>
+        <v>16.28397</v>
       </c>
       <c r="F8" t="n">
-        <v>21.71985</v>
+        <v>21.17144</v>
       </c>
       <c r="G8" t="n">
-        <v>34.19504</v>
+        <v>33.72748</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.60676</v>
+        <v>0.60855</v>
       </c>
       <c r="D10" t="n">
-        <v>1.11271</v>
+        <v>1.11986</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6008599999999999</v>
+        <v>0.59375</v>
       </c>
       <c r="D11" t="n">
-        <v>1.08831</v>
+        <v>1.09021</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.60734</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>1.13378</v>
+        <v>1.12279</v>
       </c>
     </row>
   </sheetData>
